--- a/02_Zero_Shot/outputs/NLI/roberta-large-mnli/RESULT_f-droid_roberta-large-mnli_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/NLI/roberta-large-mnli/RESULT_f-droid_roberta-large-mnli_zeroshot.xlsx
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67.26719141600006</v>
+        <v>84.78575571699912</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02367729370503346</v>
+        <v>0.02984363101619117</v>
       </c>
     </row>
   </sheetData>
